--- a/Collections/EURO/Italy/#EURO#Italy#Commemorative#[2004-present]#UNC.xlsx
+++ b/Collections/EURO/Italy/#EURO#Italy#Commemorative#[2004-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Italy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC72578-BD2F-4828-834C-000F9929E7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D488E2B-EA54-4170-A0A1-912C03448CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="85">
   <si>
     <t>Year</t>
   </si>
@@ -329,6 +332,12 @@
   </si>
   <si>
     <t>Subtype_2#Special_marks_1</t>
+  </si>
+  <si>
+    <t>200th Anniversary - Birth of Carlo Collodi</t>
+  </si>
+  <si>
+    <t>800th Anniversary - Death of Saint Francis of Assisi</t>
   </si>
 </sst>
 </file>
@@ -596,7 +605,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -731,9 +748,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1002,7 +1019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="12" customWidth="1"/>
@@ -2001,6 +2018,48 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G41" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="7">
+        <v>2026</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G42" s="10">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:F2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -2009,11 +2068,28 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="G5 G7 G9 G11:G12 G15 G17 G19 G22:G23 G25 G27">
+    <cfRule type="containsText" dxfId="16" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5 G7 G9 G11:G12 G15 G17 G19 G22:G23 G25 G27">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4 G6 G8 G10 G13:G14 G16 G18 G20:G21 G24 G26 G28">
     <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G5))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7 G5 G9 G11:G12 G15 G17 G19 G22:G23 G25 G27">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4 G6 G8 G10 G13:G14 G16 G18 G20:G21 G24 G26 G28">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2025,12 +2101,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G6 G8 G10 G13:G14 G16 G18 G20:G21 G24 G26 G28">
+  <conditionalFormatting sqref="G29">
     <cfRule type="containsText" dxfId="14" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6 G4 G8 G10 G13:G14 G16 G18 G20:G21 G24 G26 G28">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G29">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2042,13 +2118,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G29))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="G31">
+    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G31">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2059,12 +2135,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
+  <conditionalFormatting sqref="G30">
     <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G31))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G31">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G30">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2076,12 +2152,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G30">
+  <conditionalFormatting sqref="G33">
     <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G30))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G30">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G33">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2093,12 +2169,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G33">
+  <conditionalFormatting sqref="G32">
     <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G33))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G33">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2110,12 +2186,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
+  <conditionalFormatting sqref="G34">
     <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G32))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G32">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G34">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2127,12 +2203,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
+  <conditionalFormatting sqref="G36">
     <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G34))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G34">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G36">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2144,12 +2220,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
+  <conditionalFormatting sqref="G35">
     <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G36))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G36">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2161,12 +2237,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
+  <conditionalFormatting sqref="G3">
     <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G35))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G35">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2178,13 +2254,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="G37:G38">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G38">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2195,12 +2271,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G37:G38">
+  <conditionalFormatting sqref="G39:G40">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G37))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G37:G38">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G39:G40">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2212,12 +2288,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G39:G40">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(G39))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G39:G40">
+  <conditionalFormatting sqref="G41:G42">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(G41))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G41:G42">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
